--- a/participants.xlsx
+++ b/participants.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KIIT\OneDrive\Desktop\certificate_generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3474F593-CAC6-4422-BC64-97A34FEFE422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A651BDD-ADD6-43FD-900E-A4987BDF5C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D32AF330-4CF9-4AA5-8E71-C0EA126CA794}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Name</t>
   </si>
@@ -28,26 +28,67 @@
     <t>Email</t>
   </si>
   <si>
-    <t>Rajmani</t>
-  </si>
-  <si>
-    <t>24052241@kiit.ac.in</t>
+    <t>SAURABH SHEKHAR SINGH</t>
+  </si>
+  <si>
+    <t>SWAPNIL MAJUMDAR</t>
+  </si>
+  <si>
+    <t>SHREYANJAN NEOGI</t>
+  </si>
+  <si>
+    <t>PRITAM SAMANTA</t>
+  </si>
+  <si>
+    <t>Suman Das</t>
+  </si>
+  <si>
+    <t>Sumana Das</t>
+  </si>
+  <si>
+    <t>Natique Ibrar Alam</t>
+  </si>
+  <si>
+    <t>Vivan Hardasani</t>
+  </si>
+  <si>
+    <t>Mohammad Abdur Rahman</t>
+  </si>
+  <si>
+    <t>25052066@kiit.ac.in</t>
+  </si>
+  <si>
+    <t>2527029@kiit.ac.in</t>
+  </si>
+  <si>
+    <t>2505297@kiit.ac.in</t>
+  </si>
+  <si>
+    <t>2527033@kiit.ac.in</t>
+  </si>
+  <si>
+    <t>24155358@kiit.ac.in</t>
+  </si>
+  <si>
+    <t>24155359@kiit.ac.in</t>
+  </si>
+  <si>
+    <t>24052497@kiit.ac.in</t>
+  </si>
+  <si>
+    <t>23053475@kiit.ac.in</t>
+  </si>
+  <si>
+    <t>23053433@kiit.ac.in</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -63,11 +104,37 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF434343"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -77,7 +144,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,16 +156,43 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -113,21 +207,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFFFFFFF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFF8F9FA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFF8F9FA"/>
       </bottom>
       <diagonal/>
     </border>
@@ -148,13 +227,43 @@
     </border>
     <border>
       <left style="medium">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF6F8F9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FFFFFFFF"/>
       </left>
       <right style="medium">
         <color rgb="FFFFFFFF"/>
       </right>
       <top style="medium">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
         <color rgb="FFF8F9FA"/>
@@ -169,47 +278,146 @@
         <color rgb="FFFFFFFF"/>
       </right>
       <top style="medium">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="medium">
         <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF6AA84F"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -227,10 +435,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -491,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B197"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="21.08984375" customWidth="1"/>
@@ -506,798 +710,808 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" thickBot="1">
-      <c r="A2" s="9" t="s">
+    <row r="2" spans="1:2" ht="26.5" thickBot="1">
+      <c r="A2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" thickBot="1">
+      <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="2"/>
-      <c r="B3" s="4"/>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="B3" s="16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" thickBot="1">
+      <c r="A4" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" thickBot="1">
+      <c r="A5" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="A6" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" thickBot="1">
+      <c r="A7" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" thickBot="1">
+      <c r="A8" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" thickBot="1">
+      <c r="A9" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="26.5" thickBot="1">
+      <c r="A10" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="1:2" ht="21" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="3"/>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
+      <c r="A13" s="14"/>
+      <c r="B13" s="14"/>
+    </row>
+    <row r="14" spans="1:2" ht="15" thickBot="1">
+      <c r="A14" s="14"/>
+      <c r="B14" s="14"/>
+    </row>
+    <row r="15" spans="1:2" ht="15" thickBot="1">
+      <c r="A15" s="9"/>
+      <c r="B15" s="10"/>
+    </row>
+    <row r="16" spans="1:2" ht="15" thickBot="1">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+    </row>
+    <row r="17" spans="1:2" ht="15" thickBot="1">
+      <c r="A17" s="9"/>
+      <c r="B17" s="10"/>
+    </row>
+    <row r="18" spans="1:2" ht="15" thickBot="1">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+    </row>
+    <row r="19" spans="1:2" ht="15" thickBot="1">
+      <c r="A19" s="9"/>
+      <c r="B19" s="10"/>
+    </row>
+    <row r="20" spans="1:2" ht="15" thickBot="1">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+    </row>
+    <row r="21" spans="1:2" ht="15" thickBot="1">
+      <c r="A21" s="9"/>
+      <c r="B21" s="10"/>
+    </row>
+    <row r="22" spans="1:2" ht="15" thickBot="1">
+      <c r="A22" s="11"/>
+      <c r="B22" s="12"/>
+    </row>
+    <row r="23" spans="1:2" ht="15" thickBot="1">
+      <c r="A23" s="9"/>
+      <c r="B23" s="10"/>
+    </row>
+    <row r="24" spans="1:2" ht="15" thickBot="1">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+    </row>
+    <row r="25" spans="1:2" ht="15" thickBot="1">
+      <c r="A25" s="9"/>
+      <c r="B25" s="10"/>
+    </row>
+    <row r="26" spans="1:2" ht="15" thickBot="1">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
+    </row>
+    <row r="27" spans="1:2" ht="15" thickBot="1">
+      <c r="A27" s="9"/>
+      <c r="B27" s="10"/>
+    </row>
+    <row r="28" spans="1:2" ht="21" customHeight="1" thickBot="1">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
+    </row>
+    <row r="29" spans="1:2" ht="15" thickBot="1">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+    </row>
+    <row r="30" spans="1:2" ht="15" thickBot="1">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12"/>
+    </row>
+    <row r="31" spans="1:2" ht="15" thickBot="1">
+      <c r="A31" s="9"/>
+      <c r="B31" s="10"/>
+    </row>
+    <row r="32" spans="1:2" ht="15" thickBot="1">
+      <c r="A32" s="11"/>
+      <c r="B32" s="12"/>
+    </row>
+    <row r="33" spans="1:2" ht="15" thickBot="1">
+      <c r="A33" s="9"/>
+      <c r="B33" s="10"/>
+    </row>
+    <row r="34" spans="1:2" ht="15" thickBot="1">
+      <c r="A34" s="11"/>
+      <c r="B34" s="12"/>
+    </row>
+    <row r="35" spans="1:2" ht="15" thickBot="1">
+      <c r="A35" s="9"/>
+      <c r="B35" s="10"/>
+    </row>
+    <row r="36" spans="1:2" ht="15" thickBot="1">
+      <c r="A36" s="11"/>
+      <c r="B36" s="12"/>
+    </row>
+    <row r="37" spans="1:2" ht="15" thickBot="1">
+      <c r="A37" s="9"/>
+      <c r="B37" s="10"/>
+    </row>
+    <row r="38" spans="1:2" ht="15" thickBot="1">
+      <c r="A38" s="11"/>
+      <c r="B38" s="12"/>
+    </row>
+    <row r="39" spans="1:2" ht="15" thickBot="1">
+      <c r="A39" s="9"/>
+      <c r="B39" s="10"/>
+    </row>
+    <row r="40" spans="1:2" ht="15" thickBot="1">
+      <c r="A40" s="11"/>
+      <c r="B40" s="12"/>
+    </row>
+    <row r="41" spans="1:2" ht="15" thickBot="1">
+      <c r="A41" s="9"/>
+      <c r="B41" s="10"/>
+    </row>
+    <row r="42" spans="1:2" ht="15" thickBot="1">
+      <c r="A42" s="11"/>
+      <c r="B42" s="12"/>
+    </row>
+    <row r="43" spans="1:2" ht="15" thickBot="1">
+      <c r="A43" s="9"/>
+      <c r="B43" s="10"/>
+    </row>
+    <row r="44" spans="1:2" ht="15" thickBot="1">
+      <c r="A44" s="11"/>
+      <c r="B44" s="12"/>
+    </row>
+    <row r="45" spans="1:2" ht="15" thickBot="1">
+      <c r="A45" s="9"/>
+      <c r="B45" s="10"/>
+    </row>
+    <row r="46" spans="1:2" ht="15" thickBot="1">
+      <c r="A46" s="11"/>
+      <c r="B46" s="12"/>
+    </row>
+    <row r="47" spans="1:2" ht="15" thickBot="1">
+      <c r="A47" s="9"/>
+      <c r="B47" s="10"/>
+    </row>
+    <row r="48" spans="1:2" ht="15" thickBot="1">
+      <c r="A48" s="11"/>
+      <c r="B48" s="12"/>
+    </row>
+    <row r="49" spans="1:2" ht="15" thickBot="1">
+      <c r="A49" s="9"/>
+      <c r="B49" s="10"/>
+    </row>
+    <row r="50" spans="1:2" ht="15" thickBot="1">
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+    </row>
+    <row r="51" spans="1:2" ht="15" thickBot="1">
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+    </row>
+    <row r="52" spans="1:2" ht="15" thickBot="1">
+      <c r="A52" s="11"/>
+      <c r="B52" s="12"/>
+    </row>
+    <row r="53" spans="1:2" ht="15" thickBot="1">
+      <c r="A53" s="9"/>
+      <c r="B53" s="10"/>
+    </row>
+    <row r="54" spans="1:2" ht="15" thickBot="1">
+      <c r="A54" s="11"/>
+      <c r="B54" s="12"/>
+    </row>
+    <row r="55" spans="1:2" ht="15" thickBot="1">
+      <c r="A55" s="9"/>
+      <c r="B55" s="10"/>
+    </row>
+    <row r="56" spans="1:2" ht="15" thickBot="1">
+      <c r="A56" s="11"/>
+      <c r="B56" s="12"/>
+    </row>
+    <row r="57" spans="1:2" ht="15" thickBot="1">
+      <c r="A57" s="9"/>
+      <c r="B57" s="10"/>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
+      <c r="A58" s="13"/>
+      <c r="B58" s="2"/>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
+      <c r="A59" s="3"/>
+      <c r="B59" s="3"/>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
+      <c r="A61" s="3"/>
+      <c r="B61" s="3"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
+      <c r="A63" s="3"/>
+      <c r="B63" s="3"/>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
+      <c r="A65" s="3"/>
+      <c r="B65" s="3"/>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
+      <c r="A67" s="3"/>
+      <c r="B67" s="3"/>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
+      <c r="A69" s="3"/>
+      <c r="B69" s="3"/>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
+      <c r="A71" s="3"/>
+      <c r="B71" s="3"/>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
     </row>
     <row r="73" spans="1:2">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
+      <c r="A73" s="3"/>
+      <c r="B73" s="3"/>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
     </row>
     <row r="75" spans="1:2">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
+      <c r="A75" s="3"/>
+      <c r="B75" s="3"/>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
     </row>
     <row r="77" spans="1:2">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
     </row>
     <row r="79" spans="1:2">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
+      <c r="A79" s="3"/>
+      <c r="B79" s="3"/>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
     </row>
     <row r="81" spans="1:2">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
     </row>
     <row r="83" spans="1:2">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
+      <c r="A83" s="3"/>
+      <c r="B83" s="3"/>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
     </row>
     <row r="85" spans="1:2">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
     </row>
     <row r="87" spans="1:2">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
+      <c r="A87" s="3"/>
+      <c r="B87" s="3"/>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
     </row>
     <row r="89" spans="1:2">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
+      <c r="A89" s="3"/>
+      <c r="B89" s="3"/>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
     </row>
     <row r="91" spans="1:2">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
+      <c r="A91" s="3"/>
+      <c r="B91" s="3"/>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
     </row>
     <row r="93" spans="1:2">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
+      <c r="A93" s="3"/>
+      <c r="B93" s="3"/>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
+      <c r="A97" s="3"/>
+      <c r="B97" s="3"/>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
     </row>
     <row r="101" spans="1:2">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
     </row>
     <row r="103" spans="1:2">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
     </row>
     <row r="105" spans="1:2">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
     </row>
     <row r="107" spans="1:2">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
     </row>
     <row r="109" spans="1:2">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
     </row>
     <row r="111" spans="1:2">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
     </row>
     <row r="113" spans="1:2">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
     </row>
     <row r="115" spans="1:2">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
     </row>
     <row r="117" spans="1:2">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2"/>
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
     </row>
     <row r="119" spans="1:2">
-      <c r="A119" s="2"/>
-      <c r="B119" s="2"/>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
     </row>
     <row r="121" spans="1:2">
-      <c r="A121" s="2"/>
-      <c r="B121" s="2"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
     </row>
     <row r="125" spans="1:2">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
     </row>
     <row r="127" spans="1:2">
-      <c r="A127" s="2"/>
-      <c r="B127" s="2"/>
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
     </row>
     <row r="129" spans="1:2">
-      <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
     </row>
     <row r="131" spans="1:2">
-      <c r="A131" s="2"/>
-      <c r="B131" s="2"/>
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
     </row>
     <row r="133" spans="1:2">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
     </row>
     <row r="135" spans="1:2">
-      <c r="A135" s="2"/>
-      <c r="B135" s="2"/>
+      <c r="A135" s="3"/>
+      <c r="B135" s="4"/>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
     </row>
     <row r="137" spans="1:2">
-      <c r="A137" s="2"/>
-      <c r="B137" s="2"/>
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
     </row>
     <row r="139" spans="1:2">
-      <c r="A139" s="2"/>
-      <c r="B139" s="2"/>
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="1"/>
-      <c r="B140" s="3"/>
+      <c r="B140" s="1"/>
     </row>
     <row r="141" spans="1:2">
-      <c r="A141" s="2"/>
-      <c r="B141" s="2"/>
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="1"/>
-      <c r="B142" s="1"/>
+      <c r="B142" s="2"/>
     </row>
     <row r="143" spans="1:2">
-      <c r="A143" s="2"/>
-      <c r="B143" s="2"/>
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
     </row>
     <row r="145" spans="1:2">
-      <c r="A145" s="2"/>
-      <c r="B145" s="2"/>
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
     </row>
     <row r="147" spans="1:2">
-      <c r="A147" s="2"/>
-      <c r="B147" s="4"/>
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
     </row>
     <row r="149" spans="1:2">
-      <c r="A149" s="2"/>
-      <c r="B149" s="2"/>
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
     </row>
     <row r="151" spans="1:2">
-      <c r="A151" s="2"/>
-      <c r="B151" s="2"/>
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
     </row>
     <row r="153" spans="1:2">
-      <c r="A153" s="2"/>
-      <c r="B153" s="2"/>
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
     </row>
     <row r="155" spans="1:2">
-      <c r="A155" s="2"/>
-      <c r="B155" s="2"/>
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
     </row>
     <row r="157" spans="1:2">
-      <c r="A157" s="2"/>
-      <c r="B157" s="2"/>
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
     </row>
     <row r="159" spans="1:2">
-      <c r="A159" s="2"/>
-      <c r="B159" s="2"/>
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="2"/>
-      <c r="B161" s="2"/>
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="2"/>
-      <c r="B163" s="2"/>
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="2"/>
-      <c r="B165" s="2"/>
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
     </row>
     <row r="167" spans="1:2">
-      <c r="A167" s="2"/>
-      <c r="B167" s="2"/>
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
     </row>
     <row r="169" spans="1:2">
-      <c r="A169" s="2"/>
-      <c r="B169" s="2"/>
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
     </row>
     <row r="171" spans="1:2">
-      <c r="A171" s="2"/>
-      <c r="B171" s="2"/>
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
     </row>
     <row r="173" spans="1:2">
-      <c r="A173" s="2"/>
-      <c r="B173" s="2"/>
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
     </row>
     <row r="175" spans="1:2">
-      <c r="A175" s="2"/>
-      <c r="B175" s="2"/>
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
     </row>
     <row r="177" spans="1:2">
-      <c r="A177" s="2"/>
-      <c r="B177" s="2"/>
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
     </row>
     <row r="179" spans="1:2">
-      <c r="A179" s="2"/>
-      <c r="B179" s="2"/>
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
     </row>
     <row r="181" spans="1:2">
-      <c r="A181" s="2"/>
-      <c r="B181" s="2"/>
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
     </row>
     <row r="183" spans="1:2">
-      <c r="A183" s="2"/>
-      <c r="B183" s="2"/>
+      <c r="A183" s="3"/>
+      <c r="B183" s="4"/>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" s="1"/>
-      <c r="B184" s="1"/>
+      <c r="B184" s="2"/>
     </row>
     <row r="185" spans="1:2">
-      <c r="A185" s="2"/>
-      <c r="B185" s="2"/>
+      <c r="A185" s="3"/>
+      <c r="B185" s="4"/>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" s="1"/>
-      <c r="B186" s="1"/>
+      <c r="B186" s="2"/>
     </row>
     <row r="187" spans="1:2">
-      <c r="A187" s="2"/>
-      <c r="B187" s="2"/>
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" s="1"/>
-      <c r="B188" s="3"/>
+      <c r="B188" s="1"/>
     </row>
     <row r="189" spans="1:2">
-      <c r="A189" s="2"/>
-      <c r="B189" s="4"/>
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="1"/>
-      <c r="B190" s="3"/>
+      <c r="B190" s="1"/>
     </row>
     <row r="191" spans="1:2">
-      <c r="A191" s="2"/>
-      <c r="B191" s="4"/>
+      <c r="A191" s="5"/>
+      <c r="B191" s="6"/>
     </row>
     <row r="192" spans="1:2">
-      <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
-    </row>
-    <row r="193" spans="1:2">
-      <c r="A193" s="2"/>
-      <c r="B193" s="2"/>
-    </row>
-    <row r="194" spans="1:2">
-      <c r="A194" s="1"/>
-      <c r="B194" s="1"/>
-    </row>
-    <row r="195" spans="1:2">
-      <c r="A195" s="2"/>
-      <c r="B195" s="2"/>
-    </row>
-    <row r="196" spans="1:2">
-      <c r="A196" s="5"/>
-      <c r="B196" s="6"/>
-    </row>
-    <row r="197" spans="1:2">
-      <c r="A197" s="7"/>
-      <c r="B197" s="8"/>
+      <c r="A192" s="7"/>
+      <c r="B192" s="8"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{F586683B-0808-45C5-ACBC-3CB5627487DD}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>